--- a/output/pdf_financials_xlsx/CCEC.xlsx
+++ b/output/pdf_financials_xlsx/CCEC.xlsx
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.437082</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.427026</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.789357</v>
       </c>
     </row>
     <row r="93">
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-2.021554</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.429415</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-3.525036</v>
       </c>
     </row>
     <row r="119">
@@ -3071,7 +3071,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>0.437082</v>
       </c>
@@ -3726,7 +3730,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>-2.021554</v>
       </c>

--- a/output/pdf_financials_xlsx/CCEC.xlsx
+++ b/output/pdf_financials_xlsx/CCEC.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>2.5e-05</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000104</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.083577</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.666278</v>
+        <v>-1.666303</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.84196</v>
+        <v>-2.842064</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.655999</v>
+        <v>-3.739576</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.666226</v>
+        <v>-1.666251</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.841367</v>
+        <v>-2.841471</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.65511</v>
+        <v>-3.738687</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.326903</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.167721</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.090956</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.326903</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.167721</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.090956</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.438116</v>
+        <v>0.111213</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.364647</v>
+        <v>0.196926</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.147512</v>
+        <v>0.056556</v>
       </c>
     </row>
     <row r="49">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">

--- a/output/pdf_financials_xlsx/CCEC.xlsx
+++ b/output/pdf_financials_xlsx/CCEC.xlsx
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.242764</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.081869</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.368363</v>
       </c>
     </row>
     <row r="65">
@@ -1510,13 +1510,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.033436</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.2481</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.126656</v>
       </c>
     </row>
     <row r="68">
@@ -2226,10 +2226,10 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004445</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005659</v>
       </c>
     </row>
     <row r="112">
@@ -2604,10 +2604,10 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004445</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005659</v>
       </c>
     </row>
     <row r="135">
@@ -2620,10 +2620,10 @@
         <v>-1.772657</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.314201</v>
+        <v>-1.318646</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-2.6814</v>
+        <v>-2.687059</v>
       </c>
     </row>
   </sheetData>
@@ -3819,7 +3819,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
